--- a/live/YANINA_LIVE_CONTROL_CENTER_20260723.xlsx
+++ b/live/YANINA_LIVE_CONTROL_CENTER_20260723.xlsx
@@ -7,54 +7,59 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H32_Handoff" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H31_Exec" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H30_MD_Workbook" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H29_MD_Channel" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H28_TSUM_Split" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H27_BizStruct" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H25_DomainOps" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H26_Stubs" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H24_Alias" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H23_Accept" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H22_Freeze" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H21_Apply" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H20_FinanceRec" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H19_OwnerSync" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H18_Gate" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H17_Owner" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H16_OPEX" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H15_Payroll" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H14_Bridge" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H13_IM_Finance" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H12_B2B_IM" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H11_TSUM_B2B" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H10_Cash_Live" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H9_Identity_Live" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H8_DQ_Live" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H7_Controls_Live" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H6_Marts_Live" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H5_Improve_Live" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H4_Integrate_Live" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H3_New_Docs_Live" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H2_Enrichment_Live" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H1_Spine_Links_Live" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W6_TAX_BUD_Live" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W5_SUP_EXP_MAT_Live" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W4_Sales_Settle_Live" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W3_SKU_Cost_Live" sheetId="36" state="visible" r:id="rId36"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W2_Payroll_Live" sheetId="37" state="visible" r:id="rId37"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W1_Bank_Cash_Live" sheetId="38" state="visible" r:id="rId38"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_Сводка" sheetId="39" state="visible" r:id="rId39"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_Source_Catalog" sheetId="40" state="visible" r:id="rId40"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_RACI_Owners" sheetId="41" state="visible" r:id="rId41"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_Gaps_14" sheetId="42" state="visible" r:id="rId42"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Actions_57" sheetId="43" state="visible" r:id="rId43"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Retests_19" sheetId="44" state="visible" r:id="rId44"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Source_Reconcile" sheetId="45" state="visible" r:id="rId45"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_Links_Scoreboard" sheetId="46" state="visible" r:id="rId46"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_Now_Next" sheetId="47" state="visible" r:id="rId47"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_Duplicates" sheetId="48" state="visible" r:id="rId48"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stage1_ClientPack" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H36_Forensic" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H35_Scenario" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H34_CFO_PhaseC" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H33_Briefing" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H32_Handoff" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H31_Exec" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H30_MD_Workbook" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H29_MD_Channel" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H28_TSUM_Split" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H27_BizStruct" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H25_DomainOps" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H26_Stubs" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H24_Alias" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H23_Accept" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H22_Freeze" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H21_Apply" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H20_FinanceRec" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H19_OwnerSync" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H18_Gate" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H17_Owner" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H16_OPEX" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H15_Payroll" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H14_Bridge" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H13_IM_Finance" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H12_B2B_IM" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H11_TSUM_B2B" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H10_Cash_Live" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H9_Identity_Live" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H8_DQ_Live" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H7_Controls_Live" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H6_Marts_Live" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H5_Improve_Live" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H4_Integrate_Live" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H3_New_Docs_Live" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H2_Enrichment_Live" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H1_Spine_Links_Live" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W6_TAX_BUD_Live" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W5_SUP_EXP_MAT_Live" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W4_Sales_Settle_Live" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W3_SKU_Cost_Live" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W2_Payroll_Live" sheetId="42" state="visible" r:id="rId42"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W1_Bank_Cash_Live" sheetId="43" state="visible" r:id="rId43"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_Сводка" sheetId="44" state="visible" r:id="rId44"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_Source_Catalog" sheetId="45" state="visible" r:id="rId45"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_RACI_Owners" sheetId="46" state="visible" r:id="rId46"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_Gaps_14" sheetId="47" state="visible" r:id="rId47"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Actions_57" sheetId="48" state="visible" r:id="rId48"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Retests_19" sheetId="49" state="visible" r:id="rId49"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Source_Reconcile" sheetId="50" state="visible" r:id="rId50"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_Links_Scoreboard" sheetId="51" state="visible" r:id="rId51"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_Now_Next" sheetId="52" state="visible" r:id="rId52"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_Duplicates" sheetId="53" state="visible" r:id="rId53"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -547,39 +552,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>H32 Project Handoff</t>
+          <t>Stage 1 Client Pack</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-24 19:38</t>
+          <t>2026-07-27 12:51</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H32: project handoff published (HANDOFF.md). Autonomous data work paused until commit or new files.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Doc</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>HANDOFF.md</t>
+          <t>live/client_pack/ — comprehensive diagnostic deliverables</t>
         </is>
       </c>
     </row>
@@ -594,83 +587,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>H23 RACI ACCEPT</t>
+          <t>H28 TSUM COGS split</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-24 19:21</t>
+          <t>2026-07-24 19:32</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H23: RACI ACCEPT on 8 named rows; 10 still OPEN_NEEDS_OWNER; H21 flags upgraded (10 lines); recommendations ACCEPT=5. Domain-owned staging — not full SoT.</t>
+          <t>H28: TSUM dual view — reported margin 37.9% vs product(W3) 87.9%; commission proxy 60,954,243 ₽ (~50.1% rev) vs agency@net-rate 65,503,234 ₽. No double-count policy set.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Accepted rows</t>
+          <t>Reported GM%</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Open needs FIO</t>
+          <t>Product GM%</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>87.90000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>H21 flags</t>
+          <t>Comm proxy / Agency model</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>OWNER_ACCEPTED</t>
+          <t>60,954,243 / 65,503,234</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SoT?</t>
+          <t>Doc</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Domain-owned staging (not full SoT)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Policy</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>live/SOT_POLICY.md</t>
+          <t>live/TSUM_COGS_SPLIT.md</t>
         </is>
       </c>
     </row>
@@ -685,75 +666,63 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>H22 Staging Freeze</t>
+          <t>H27 Business Structure</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-24 19:06</t>
+          <t>2026-07-24 19:29</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H22 staging freeze: invariants 9/9 PASS. Status=FROZEN_AWAITING_OWNER. Autonomous path closed.</t>
+          <t>H27: business structure ingested; 10 RACI stubs→real FIO; 7 model flags (P0: TSUM commission in COGS; channel mix 83/8/9; Decor wind-down). See live/BUSINESS_STRUCTURE.md</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Doc</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FROZEN_AWAITING_OWNER</t>
+          <t>live/BUSINESS_STRUCTURE.md</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Invariants</t>
+          <t>P0 flag</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>9/9</t>
+          <t>TSUM commission inside COGS</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Stop</t>
+          <t>Channel mix 2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>No H23+ without owner input</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Doc</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>live/STAGING_FREEZE.md</t>
+          <t>83% individual / 8% IM / 9% B2B(TSUM)</t>
         </is>
       </c>
     </row>
@@ -774,65 +743,63 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>H21 Apply H20 provisional</t>
+          <t>H25 Domain Ops</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-24 18:12</t>
+          <t>2026-07-24 19:29</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H21: provisional flags on 9 sales lines / 4 SKUs; reported GM 52.9% → clean(ex wholesale loss) 53.0%. Quarantine 0-3243 kept. RACI untouched.</t>
+          <t>H25: 14 gap rows → 14 assigned (real=14, stub=0), open=0. Open domain asks: 0.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Reported GM%</t>
+          <t>Gap rows</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52.9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Clean GM% (ex wholesale loss)</t>
+          <t>Assigned (accepted owners)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>53</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RACI touched?</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+          <t>Need open-domain FIO</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SoT?</t>
+          <t>Pack</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>live/YANINA_DOMAIN_OPS_H25.xlsx</t>
         </is>
       </c>
     </row>
@@ -847,63 +814,49 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>H20 Finance Recommendations</t>
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>H26 Temporary Owner Stubs</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-24 17:46</t>
+          <t>2026-07-24 19:26</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H20: proposed OK_COMMERCIAL_LOSS for 0-2493A/2496/2497 (combined margin impact -45,095 ₽); KEEP_QUARANTINE for 0-3243. COGS unchanged.</t>
+          <t>H26: 10 RACI stubs (ACCEPT_STUB); alias candidates under Product stub; domain board rebuilt — 14/14 gaps have owner fio (2 on stubs). Replace stubs with real FIO.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Doc</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>live/FINANCE_RECOMMENDATIONS.md</t>
-        </is>
+          <t>Stubs applied</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Packet sheet</t>
+          <t>Replace with real FIO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>RECOMMENDATIONS_H20</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Applied to COGS?</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>YES — required</t>
         </is>
       </c>
     </row>
@@ -918,64 +871,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>H19 Owner Packet Sync</t>
+          <t>H24 SKU Alias Master</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-24 17:44</t>
+          <t>2026-07-24 19:22</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H19: Owner Packet synced — sheets H17_ACTIONS(10), H18_BLOCKED(12), DATA_REQUESTS_NOW(8), DECISION_LOG. RACI decision cells still empty (0 filled).</t>
+          <t>H24: sku_alias_master created — 16 controlled candidates (pending Product Owner), 4 accepted exception/quarantine rows from H23.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Packet</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>live/YANINA_OWNER_PACKET_RACI_AND_REQUESTS.xlsx</t>
-        </is>
+          <t>Candidates</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>New sheets</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>H17_ACTIONS | H18_BLOCKED | DATA_REQUESTS_NOW | DECISION_LOG</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>RACI ACCEPT filled?</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>NO (intentionally)</t>
-        </is>
+          <t>Accepted rows</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -989,73 +926,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>H18 Controls Release Gate</t>
+          <t>H23 RACI ACCEPT</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-24 17:42</t>
+          <t>2026-07-24 19:21</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H18: provisional release gate — RELEASED 18/30, BLOCKED 12/30. Top fails: IM_ACQ_COMBO:6, BANK_DDS_CORE:5, TSUM_NET_MODEL:2, TAX_CASH_BANK:1. B2B settle (info): PARTIAL 39/54 (open=15).</t>
+          <t>H23: RACI ACCEPT on 8 named rows; 10 still OPEN_NEEDS_OWNER; H21 flags upgraded (10 lines); recommendations ACCEPT=5. Domain-owned staging — not full SoT.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RELEASED</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>18/30</t>
-        </is>
+          <t>Accepted rows</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>12/30</t>
-        </is>
+          <t>Open needs FIO</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Blocked %</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>40</v>
+          <t>H21 flags</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>OWNER_ACCEPTED</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Top fail controls</t>
+          <t>SoT?</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IM_ACQ_COMBO:6, BANK_DDS_CORE:5, TSUM_NET_MODEL:2, TAX_CASH_BANK:1</t>
+          <t>Domain-owned staging (not full SoT)</t>
         </is>
       </c>
     </row>
@@ -1067,19 +1002,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PROVISIONAL_H18 (not SoT)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Docs</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>live/RELEASE_GATE.md</t>
+          <t>live/SOT_POLICY.md</t>
         </is>
       </c>
     </row>
@@ -1094,119 +1017,75 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>H17 Owner Action Pack</t>
+          <t>H22 Staging Freeze</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-24 17:39</t>
+          <t>2026-07-24 19:06</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H17: 10 owner actions (P0 RACI + P1 finance/SKU + P2 data requests); B2B open request 15 (~2.51M); finance evidence 8 lines; SKU alias candidates 16. Not SoT.</t>
+          <t>H22 staging freeze: invariants 9/9 PASS. Status=FROZEN_AWAITING_OWNER. Autonomous path closed.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Actions</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>10</v>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>FROZEN_AWAITING_OWNER</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P0/P1/P2/P3</t>
+          <t>Invariants</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1/4/3/2</t>
+          <t>9/9</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B2B open</t>
+          <t>Stop</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>15 / 2,514,023 ₽</t>
+          <t>No H23+ without owner input</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alias candidates</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Pack xlsx</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>live/YANINA_OWNER_ACTION_PACK_H17.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Checklist md</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>live/OWNER_ACTIONS.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Evidence</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>live/evidence/h17_owner_pack_20260724/</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Next human</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Fill decision_ACCEPT_REJECT in Owner Packet (A-RACI-01)</t>
+          <t>Doc</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>live/STAGING_FREEZE.md</t>
         </is>
       </c>
     </row>
@@ -1221,51 +1100,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
-        <is>
-          <t>H16 OPEX multi</t>
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>H21 Apply H20 provisional</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-24 17:36</t>
+          <t>2026-07-24 18:12</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H16: OPEX multi CLOSE/SOFT 30/30 (clean↔bank 25, DDS↔bank 29; raw was ~40%). SKU residual: quarantine 0-3243 kept; watch priority 9 SKU.</t>
+          <t>H21: provisional flags on 9 sales lines / 4 SKUs; reported GM 52.9% → clean(ex wholesale loss) 53.0%. Quarantine 0-3243 kept. RACI untouched.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>30/30</t>
-        </is>
+          <t>Reported GM%</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>52.9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Clean↔bank</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>25/30</t>
+          <t>Clean GM% (ex wholesale loss)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>RACI touched?</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SoT?</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -1284,59 +1183,59 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
-        <is>
-          <t>H15 Payroll multi</t>
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>H20 Finance Recommendations</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-24 17:25</t>
+          <t>2026-07-24 17:46</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H15: payroll multi-recon CLOSE/SOFT overall 30/30; expense↔DDS 17/30; DDS↔bank 29/30 (was ~2/30 on lines-only).</t>
+          <t>H20: proposed OK_COMMERCIAL_LOSS for 0-2493A/2496/2497 (combined margin impact -45,095 ₽); KEEP_QUARANTINE for 0-3243. COGS unchanged.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CLOSE/SOFT overall</t>
+          <t>Doc</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30/30</t>
+          <t>live/FINANCE_RECOMMENDATIONS.md</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DDS↔bank</t>
+          <t>Packet sheet</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>29/30</t>
+          <t>RECOMMENDATIONS_H20</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Plan doc</t>
+          <t>Applied to COGS?</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>live/RESULTS_AND_NEXT_PLAN.md</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -1351,69 +1250,63 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
-        <is>
-          <t>H14 Operating Bridge</t>
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>H19 Owner Packet Sync</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-24 16:50</t>
+          <t>2026-07-24 17:44</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H14: operating bridge 30m; gross margin 53.1% → operating -58.0% (-111,889,748 ₽); opex buckets classified; controls dashboard 6 series.</t>
+          <t>H19: Owner Packet synced — sheets H17_ACTIONS(10), H18_BLOCKED(12), DATA_REQUESTS_NOW(8), DECISION_LOG. RACI decision cells still empty (0 filled).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Gross %</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>53.1</v>
+          <t>Packet</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>live/YANINA_OWNER_PACKET_RACI_AND_REQUESTS.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Operating %</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>-58</v>
+          <t>New sheets</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>H17_ACTIONS | H18_BLOCKED | DATA_REQUESTS_NOW | DECISION_LOG</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Operating ₽</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>-111889747.95</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>+/- months</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>1/29</t>
+          <t>RACI ACCEPT filled?</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>NO (intentionally)</t>
         </is>
       </c>
     </row>
@@ -1428,39 +1321,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>H31 Executive + MD recon fix</t>
+          <t>H36 Forensic Salon Sber</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-24 19:38</t>
+          <t>2026-07-24 20:50</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H31: 2024-01 → CLOSE after excluding Казьмина −70k adj; 2026-06 → DDS_LAG; MD recon ≥2024 CLOSE+SOFT 29/30 (+1 lag). Executive dashboard published.</t>
+          <t>H36 forensic: fresh Salon Sber (24.07) 510 rows = exact coverage of bank LE-OOO-SALON (510). date|amount match 510/510. Ingest NOT needed. BANK_DDS BLOCKED not due to missing Salon extract. Consulting STOP until owner input.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Doc</t>
+          <t>Match</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>live/EXEC_DASHBOARD.md</t>
+          <t>510/510</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>FRESH_ALREADY_COVERED</t>
         </is>
       </c>
     </row>
@@ -1475,60 +1380,98 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
-        <is>
-          <t>H13 IM combo + finance</t>
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>H18 Controls Release Gate</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-24 16:48</t>
+          <t>2026-07-24 17:42</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H13: IM combo CLOSE/SOFT 24/30 (IP-only was 19); quarantine 1 COGS lines (0-3243); neg SKUs now 3; margin 53.1%.</t>
+          <t>H18: provisional release gate — RELEASED 18/30, BLOCKED 12/30. Top fails: IM_ACQ_COMBO:6, BANK_DDS_CORE:5, TSUM_NET_MODEL:2, TAX_CASH_BANK:1. B2B settle (info): PARTIAL 39/54 (open=15).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IM CLOSE/SOFT</t>
+          <t>RELEASED</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Neg SKUs</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>3</v>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>12/30</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Margin %</t>
+          <t>Blocked %</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>53.1</v>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Top fail controls</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>IM_ACQ_COMBO:6, BANK_DDS_CORE:5, TSUM_NET_MODEL:2, TAX_CASH_BANK:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Policy</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>PROVISIONAL_H18 (not SoT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>live/RELEASE_GATE.md</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1542,51 +1485,119 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
-        <is>
-          <t>H12 B2B + IM lag</t>
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>H17 Owner Action Pack</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-24 16:46</t>
+          <t>2026-07-24 17:39</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H12: B2B 39 linked / 15 open (open rev 2,514,023 ₽); special +2; IM best-lag CLOSE/SOFT 19/30 (lag0 14).</t>
+          <t>H17: 10 owner actions (P0 RACI + P1 finance/SKU + P2 data requests); B2B open request 15 (~2.51M); finance evidence 8 lines; SKU alias candidates 16. Not SoT.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B2B</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>39/15</t>
-        </is>
+          <t>Actions</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IM CLOSE/SOFT</t>
+          <t>P0/P1/P2/P3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>1/4/3/2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>B2B open</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>15 / 2,514,023 ₽</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Alias candidates</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Pack xlsx</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>live/YANINA_OWNER_ACTION_PACK_H17.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Checklist md</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>live/OWNER_ACTIONS.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>live/evidence/h17_owner_pack_20260724/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Next human</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Fill decision_ACCEPT_REJECT in Owner Packet (A-RACI-01)</t>
         </is>
       </c>
     </row>
@@ -1601,71 +1612,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>H11 TSUM net + B2B multi</t>
+          <t>H16 OPEX multi</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-24 16:43</t>
+          <t>2026-07-24 17:36</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H11: TSUM net-rate 0.4668 → CLOSE/SOFT vs model 28/30; B2B multi-pay +14 (full 3, partial 11) → linked 34/open 20.</t>
+          <t>H16: OPEX multi CLOSE/SOFT 30/30 (clean↔bank 25, DDS↔bank 29; raw was ~40%). SKU residual: quarantine 0-3243 kept; watch priority 9 SKU.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TSUM net-rate</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>0.4668</v>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>30/30</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TSUM CLOSE/SOFT model</t>
+          <t>Clean↔bank</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>28/30</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>B2B newly</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>B2B linked/open</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>34/20</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -1680,78 +1671,64 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>H10 Channel Cash</t>
+          <t>H15 Payroll multi</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-24 16:41</t>
+          <t>2026-07-24 17:25</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H10: B2B +7 HIGH links (B2B 20 linked / 34 open); IM↔ACQ(IP) cov 0.889 CLOSE/SOFT 14/30; TSUM↔agent cov 0.469 CLOSE/SOFT 7/30; SKU registry 20.</t>
+          <t>H15: payroll multi-recon CLOSE/SOFT overall 30/30; expense↔DDS 17/30; DDS↔bank 29/30 (was ~2/30 on lines-only).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B2B +</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>7</v>
+          <t>CLOSE/SOFT overall</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>30/30</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IM IP cov</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.889</v>
+          <t>DDS↔bank</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>29/30</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TSUM cov</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.469</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>IM CLOSE/SOFT</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>TSUM CLOSE/SOFT</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>7</v>
+          <t>Plan doc</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>live/RESULTS_AND_NEXT_PLAN.md</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1771,62 +1748,64 @@
     <row r="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>H9 Cost Identity</t>
+          <t>H14 Operating Bridge</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-24 16:36</t>
+          <t>2026-07-24 16:50</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H9b: +62 category-mismatch COGS fixes; neg SKUs now 4; margin 53.1%; total collision fixes 67.</t>
+          <t>H14: operating bridge 30m; gross margin 53.1% → operating -58.0% (-111,889,748 ₽); opex buckets classified; controls dashboard 6 series.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Total collision fixes</t>
+          <t>Gross %</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>67</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Margin %</t>
+          <t>Operating %</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>53.1</v>
+        <v>-58</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Neg SKUs</t>
+          <t>Operating ₽</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>-111889747.95</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Watchlist SKUs</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>75</v>
+          <t>+/- months</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1/29</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1840,57 +1819,60 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>H8 DQ</t>
+          <t>H13 IM combo + finance</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-24 16:33</t>
+          <t>2026-07-24 16:48</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>finding</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>H8 DQ: cleared 0 inflated W3 costs, junk 683; neg SKUs 5→5; margin 51.5%→51.5% (costed).</t>
+          <t>H13: IM combo CLOSE/SOFT 24/30 (IP-only was 19); quarantine 1 COGS lines (0-3243); neg SKUs now 3; margin 53.1%.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>neg_skus</t>
+          <t>IM CLOSE/SOFT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5→5</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>margin_pct</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>51.5→51.5</t>
-        </is>
+          <t>Neg SKUs</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Margin %</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>53.1</v>
       </c>
     </row>
   </sheetData>
@@ -1904,235 +1886,52 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>H7 Controls — card / entity / recon / anomalies</t>
+          <t>H12 B2B + IM lag</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-24 16:30</t>
+          <t>2026-07-24 16:46</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>finding</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>H7: card out 7675485 RUB (OTHER:37.7%, TRAVEL:29.4%, MARKETPLACE:18.5%, OFFICE_SUPPLY:9.3%); core↔DDS CLOSE/SOFT 25; Salon out 5516594; margin anomalies 16 (neg SKU 14).</t>
+          <t>H12: B2B 39 linked / 15 open (open rev 2,514,023 ₽); special +2; IM best-lag CLOSE/SOFT 19/30 (lag0 14).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>39/15</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Card categories</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>amount_rub</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>share_pct</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>payments</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2891710.68</v>
-      </c>
-      <c r="C8" t="n">
-        <v>37.7</v>
-      </c>
-      <c r="D8" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>TRAVEL</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>2259561</v>
-      </c>
-      <c r="C9" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="D9" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>MARKETPLACE</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1421377.94</v>
-      </c>
-      <c r="C10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="D10" t="n">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>OFFICE_SUPPLY</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>711606.15</v>
-      </c>
-      <c r="C11" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="D11" t="n">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>FOOD</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>233299.94</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3</v>
-      </c>
-      <c r="D12" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>TAXI_DELIVERY</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>157929.44</v>
-      </c>
-      <c r="C13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="D13" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Entity bank</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>legal_entity_id</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>out_rub</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>in_rub</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>net_rub</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>LE-IP-YANINA</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>162676418.86</v>
-      </c>
-      <c r="C18" t="n">
-        <v>253950029.63</v>
-      </c>
-      <c r="D18" t="n">
-        <v>91273610.77</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>LE-OOO-DEKOR</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>35642961.16</v>
-      </c>
-      <c r="C19" t="n">
-        <v>35620577.4</v>
-      </c>
-      <c r="D19" t="n">
-        <v>-22383.76</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>LE-OOO-SALON-YANINA</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>5516593.99</v>
-      </c>
-      <c r="C20" t="n">
-        <v>4923673.51</v>
-      </c>
-      <c r="D20" t="n">
-        <v>-592920.48</v>
+          <t>IM CLOSE/SOFT</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>19/30</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2146,160 +1945,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>H6 Marts</t>
+          <t>H11 TSUM net + B2B multi</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-24 16:27</t>
+          <t>2026-07-24 16:43</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>overall_margin_pct</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>47.9</v>
+          <t>H11: TSUM net-rate 0.4668 → CLOSE/SOFT vs model 28/30; B2B multi-pay +14 (full 3, partial 11) → linked 34/open 20.</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>overall_margin_rub</t>
+          <t>TSUM net-rate</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>92464727.29000001</v>
+        <v>0.4668</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>revenue_costed</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>192918905.92</v>
+          <t>TSUM CLOSE/SOFT model</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>28/30</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>settle_linked</t>
+          <t>B2B newly</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>38</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>finding</t>
+          <t>B2B linked/open</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>H6: margin overall 47.9% on 193482540 RUB; warehouses 9 qty_end=967.0; settle linked 38 (+0 H6).</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>channel</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>revenue_rub</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>margin_pct</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>cogs_coverage</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>B2B</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>13897226.09</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>68.3</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>IM</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>56736038.01</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>70.2</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>0.923</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>TSUM</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>122849275.56</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>35.4</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>1.0</t>
+          <t>34/20</t>
         </is>
       </c>
     </row>
@@ -2314,133 +2024,78 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>H5 — stock cost + alias relink + Sber Salon tax</t>
+          <t>H10 Channel Cash</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-24 16:25 | Controlled Staging</t>
+          <t>2026-07-24 16:41</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>Метрика</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>Значение</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>H10: B2B +7 HIGH links (B2B 20 linked / 34 open); IM↔ACQ(IP) cov 0.889 CLOSE/SOFT 14/30; TSUM↔agent cov 0.469 CLOSE/SOFT 7/30; SKU registry 20.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>stock_cost lines</t>
+          <t>B2B +</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2957</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>derived costs +W3</t>
+          <t>IM IP cov</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>720</v>
+        <v>0.889</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>W4 cost links</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>1408 → 2696 (+1288)</t>
-        </is>
+          <t>TSUM cov</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.469</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SKU ∩ cost∩sales</t>
+          <t>IM CLOSE/SOFT</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>901</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SKU in_cost / in_sales</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>1315 / 901</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>stock by WH rows</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Sber Salon tax pays</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>10 / 520475.27 RUB</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>evidence</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>live/evidence/h5_improve_20260724/</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>finding</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>H5: stock_cost 2957 lines / +720 derived costs; W4 cost links 1408→2696 (+1288); SKU∩ 901; Sber Salon tax 10 pays ~520475.27 RUB.</t>
-        </is>
+          <t>TSUM CLOSE/SOFT</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2454,155 +2109,68 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>H4 — интеграция новых продаж/SKU/тканей в W3/W4/W5</t>
+          <t>H9 Cost Identity</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-24 16:21 | Controlled Staging</t>
+          <t>2026-07-24 16:36</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>Метрика</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>Значение</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>H9b: +62 category-mismatch COGS fixes; neg SKUs now 4; margin 53.1%; total collision fixes 67.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>W4 sales lines</t>
+          <t>Total collision fixes</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2826</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>W4 by channel</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>{"B2B": 230, "IM": 1852, "TSUM": 744}</t>
-        </is>
+          <t>Margin %</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>53.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>W4 revenue RUB</t>
+          <t>Neg SKUs</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>193482539.66</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>W4 settlements / bank-linked</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>806 / 33</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>W4 lines with W3 cost</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1408</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>SKU master ∩ cost∩sales</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>SKU in cost / in sales</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>368 / 738</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fabric SKUs</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1728</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Fabric warehouse end RUB</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>{"warehouse": "Склад Мокеева", "in_rub": 12520673.4, "out_rub": 11129885.29, "end_rub": 1390788.11}</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>evidence</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>live/evidence/h4_integrate_20260724/</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>finding</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>H4: W4 refresh 2826 sales / 806 settlements (33 bank-linked); SKU cover cost 368/sales 738/∩ 257; fabric SKUs 1728 end~None.</t>
-        </is>
+          <t>Watchlist SKUs</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -2616,49 +2184,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>H30 MD workbook parse</t>
+          <t>H35 Scenario + Day7</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-24 19:37</t>
+          <t>2026-07-24 20:36</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H30: MD workbook parsed — payments 6663, salon 4194, shop 11173; 2025 payments 2,319,617 EUR vs DDS Salon+Shop 2,325,846 (gap -6,229); recon CLOSE+SOFT 28/30 since 2024.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2025 gap EUR</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>-6229</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Doc</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>live/MD_WORKBOOK.md</t>
+          <t>H35: Illustrative 2025 anti-example (MD 232.6M + goods 72.9M; goods-only -74% is artifact); Merkushina questionnaire; Day-7 scorecard all MISSING; optional Salon Sber note without ingest.</t>
         </is>
       </c>
     </row>
@@ -2673,168 +2219,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>H3 — 14 новых документов</t>
+          <t>H8 DQ</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-24 16:18 | Controlled Staging | NEW LE Салон Юлия Янина</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>Метрика</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>Значение</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>finding</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>H8 DQ: cleared 0 inflated W3 costs, junk 683; neg SKUs 5→5; margin 51.5%→51.5% (costed).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>catalog</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>107</v>
+          <t>neg_skus</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>5→5</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>margin_pct</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LE-IP-YANINA, LE-OOO-DEKOR, LE-OOO-SALON-YANINA</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Sber payments</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Sber OUT/IN RUB</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>5516593.99 / 4923673.51</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Card StatementFull</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>417 | ['Мамушкина Е.А.']</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>SKU master</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1863</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Sales lines B2B/IM/TSUM</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>{"B2B": 230, "IM": 1852, "TSUM": 744}</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Sales revenue RUB</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>{"B2B": 13897226.09, "IM": 56736038.01, "TSUM": 122849275.56}</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Fabric end stock RUB</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>23502565.09</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>RACI draft</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Мамушкина Елена / Сливяк Галина — нужен ACCEPT</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>evidence</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>live/evidence/h3_new_docs_20260724/</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>finding</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>H3: +14 files → catalog 107; NEW LE Салон Янина; Sber 510 pays; card 417 (holder Мамушкина); SKU master 1863; sales ext 2826; RACI draft Мамушкина/Сливяк.</t>
+          <t>51.5→51.5</t>
         </is>
       </c>
     </row>
@@ -2849,127 +2283,235 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>H2 Enrichment — USN amounts + settle backfill + signer candidates</t>
+          <t>H7 Controls — card / entity / recon / anomalies</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Updated: 2026-07-24 16:12 | NOT SoT | RACI still required</t>
+          <t>2026-07-24 16:30</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>Метрика</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>Значение</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>settle backfill</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>{"applied": 8, "by_conf": {"HIGH": 6, "MED": 2}}</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>finding</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>H7: card out 7675485 RUB (OTHER:37.7%, TRAVEL:29.4%, MARKETPLACE:18.5%, OFFICE_SUPPLY:9.3%); core↔DDS CLOSE/SOFT 25; Salon out 5516594; margin anomalies 16 (neg SKU 14).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SUP fuzzy HIGH</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>{"candidates": 2, "by_conf": {"HIGH": 2}, "out_rub": 73929.52}</t>
+          <t>Card categories</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>USN amounts extracted</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>4/4</t>
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>amount_rub</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>share_pct</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>payments</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>signer candidates</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>ЯНИН ЕВГЕНИЙ НИКОЛАЕВИЧ, ЯНИНА ЮЛИЯ ФЕДОРОВНА</t>
-        </is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2891710.68</v>
+      </c>
+      <c r="C8" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="D8" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>usn obligations patched</t>
+          <t>TRAVEL</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>2259561</v>
+      </c>
+      <c r="C9" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>evidence</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>live/evidence/h2_enrichment_20260724/</t>
-        </is>
+          <t>MARKETPLACE</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1421377.94</v>
+      </c>
+      <c r="C10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>172</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>finding</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>H2: settle backfill {'applied': 8, 'by_conf': {'HIGH': 6, 'MED': 2}}; SUP fuzzy {'candidates': 2, 'by_conf': {'HIGH': 2}, 'out_rub': 73929.52}; USN amounts 4/4; signer candidates ['ЯНИН ЕВГЕНИЙ НИКОЛАЕВИЧ', 'ЯНИНА ЮЛИЯ ФЕДОРОВНА'].</t>
-        </is>
+          <t>OFFICE_SUPPLY</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>711606.15</v>
+      </c>
+      <c r="C11" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>54</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>next</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Confirm signer candidate(s) in Owner Packet → fill RACI → SoT gate</t>
-        </is>
+          <t>FOOD</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>233299.94</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TAXI_DELIVERY</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>157929.44</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Entity bank</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>legal_entity_id</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>out_rub</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>in_rub</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>net_rub</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>LE-IP-YANINA</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>162676418.86</v>
+      </c>
+      <c r="C18" t="n">
+        <v>253950029.63</v>
+      </c>
+      <c r="D18" t="n">
+        <v>91273610.77</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>LE-OOO-DEKOR</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>35642961.16</v>
+      </c>
+      <c r="C19" t="n">
+        <v>35620577.4</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-22383.76</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>LE-OOO-SALON-YANINA</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>5516593.99</v>
+      </c>
+      <c r="C20" t="n">
+        <v>4923673.51</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-592920.48</v>
       </c>
     </row>
   </sheetData>
@@ -2983,134 +2525,160 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>H1 Spine Links — post W1–W6 hardening</t>
+          <t>H6 Marts</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Updated: 2026-07-24 16:08 | NOT SoT</t>
+          <t>2026-07-24 16:27</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>Метрика</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>Значение</t>
-        </is>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>overall_margin_pct</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>47.9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SUP with INN matched in bank</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>28/44</t>
-        </is>
+          <t>overall_margin_rub</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>92464727.29000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SUP payment edges (OUT)</t>
+          <t>revenue_costed</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>304</v>
+        <v>192918905.92</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SUP matched OUT RUB</t>
+          <t>settle_linked</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>54740292.94</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SETTLE↔bank by doc_num</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>by confidence</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>{"LOW": 6, "HIGH": 6, "MED": 2}</t>
+          <t>finding</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>H6: margin overall 47.9% on 193482540 RUB; warehouses 9 qty_end=967.0; settle linked 38 (+0 H6).</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>evidence</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>live/evidence/h1_spine_links_20260724/</t>
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>channel</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>revenue_rub</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>margin_pct</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>cogs_coverage</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>finding</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>H1: SUP.inn↔bank 28/44 INN, 304 out edges (~54740293 RUB); SETTLE↔bank by doc_num: 6 ({'LOW': 6}).</t>
+          <t>13897226.09</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>68.3</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>next</t>
+          <t>IM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>H1: SUP.inn↔bank 28/44 INN, 304 out edges (~54740293 RUB); SETTLE↔bank by doc_num: 14 ({'LOW': 6, 'HIGH': 6, 'MED': 2}).</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>by_method</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>{"doc_num_in_purpose": 6, "amount_name_same_month": 8}</t>
+          <t>56736038.01</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>70.2</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>0.923</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TSUM</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>122849275.56</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>35.4</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1.0</t>
         </is>
       </c>
     </row>
@@ -3125,20 +2693,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>YANINA W6 TAX/BUD — Controlled Staging</t>
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>H5 — stock cost + alias relink + Sber Salon tax</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Updated: 2026-07-24 16:04 | NOT SoT — RACI gate still blocks</t>
+          <t>2026-07-24 16:25 | Controlled Staging</t>
         </is>
       </c>
     </row>
@@ -3157,690 +2725,100 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>tax_obligations</t>
+          <t>stock_cost lines</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25</v>
+        <v>2957</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>tax_by_type</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>{"6NDFL": 5, "NDS": 5, "USN": 4, "RSV": 6, "ENS": 2, "REPORT_LIST": 3}</t>
-        </is>
+          <t>derived costs +W3</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>720</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DEKOR INN</t>
+          <t>W4 cost links</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7735518240</t>
+          <t>1408 → 2696 (+1288)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>tax_cash_lines</t>
+          <t>SKU ∩ cost∩sales</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>901</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>bank_tax_budget_payments</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>210</v>
+          <t>SKU in_cost / in_sales</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1315 / 901</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>tax_cash↔bank</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>{"GAP": 1, "CLOSE": 26, "SOFT_GAP": 3}</t>
-        </is>
+          <t>stock by WH rows</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>564</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>tax CLOSE/SOFT months</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>29</v>
+          <t>Sber Salon tax pays</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>10 / 520475.27 RUB</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>budget_lines</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>475</v>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>live/evidence/h5_improve_20260724/</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>bud_exp↔DDS</t>
+          <t>finding</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{"DDS_ONLY": 25, "CLOSE": 2, "SOFT_GAP": 1, "GAP": 2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>bud CLOSE/SOFT</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-01, 2026-02, 2026-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>bud_payroll↔W2</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>{"GAP": 2, "SOFT_GAP": 2, "CLOSE": 1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>evidence</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>live/evidence/w6_tax_bud_20260724/</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>registers</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>live/registers/w6_tax_bud/</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>finding</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>W6: 25 tax obligations ({'6NDFL': 5, 'NDS': 5, 'USN': 4, 'RSV': 6, 'ENS': 2, 'REPORT_LIST': 3}); tax_cash↔bank: {'GAP': 1, 'CLOSE': 26, 'SOFT_GAP': 3}; budget 475 lines; bud_exp↔DDS: {'DDS_ONLY': 25, 'CLOSE': 2, 'SOFT_GAP': 1, 'GAP': 2}; bud_payroll↔W2: {'GAP': 2, 'SOFT_GAP': 2, 'CLOSE': 1}.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>next</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>RACI/SoT gate; optional deep PDF amount extract; SUP.inn→bank match</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>recon_tax_cash_bank (sample recent)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>period_month</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>tax_cash_rub</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>bank_tax_like_rub</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>delta</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>444228.63</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>444228.63</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>CLOSE</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2025-02</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>741644.66</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>741644.66</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>CLOSE</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2025-03</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>883006.92</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>878906.92</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>4100.0</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>CLOSE</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2025-04</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>3809031.94</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>3804197.94</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>4834.0</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>CLOSE</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2025-05</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>599816.64</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>599816.64</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>CLOSE</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>775148.87</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>775148.87</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>CLOSE</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2025-07</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2948598.18</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>2906598.18</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>42000.0</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>CLOSE</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2025-08</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>1470436.95</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>1393026.95</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>77410.0</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>SOFT_GAP</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2025-09</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>1267928.63</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>1267928.63</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>CLOSE</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>2025-10</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2257284.46</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>2221784.46</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>35500.0</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>CLOSE</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>2025-11</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>1528446.62</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>1528446.62</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>CLOSE</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2025-12</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>1828724.89</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>1828724.89</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>CLOSE</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>1718264.68</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>1672113.41</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>46151.27</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>CLOSE</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>475944.0</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>475944.0</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>CLOSE</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>3201097.69</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>3201097.69</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>CLOSE</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>4076718.89</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>4076718.89</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>CLOSE</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>1646534.41</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>1646534.41</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>CLOSE</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>288670.11</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>319570.11</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>-30900.0</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>SOFT_GAP</t>
+          <t>H5: stock_cost 2957 lines / +720 derived costs; W4 cost links 1408→2696 (+1288); SKU∩ 901; Sber Salon tax 10 pays ~520475.27 RUB.</t>
         </is>
       </c>
     </row>
@@ -3850,6 +2828,1350 @@
 </file>
 
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>H4 — интеграция новых продаж/SKU/тканей в W3/W4/W5</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-24 16:21 | Controlled Staging</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Метрика</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Значение</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>W4 sales lines</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2826</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>W4 by channel</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>{"B2B": 230, "IM": 1852, "TSUM": 744}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>W4 revenue RUB</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>193482539.66</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>W4 settlements / bank-linked</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>806 / 33</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>W4 lines with W3 cost</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SKU master ∩ cost∩sales</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SKU in cost / in sales</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>368 / 738</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Fabric SKUs</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1728</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Fabric warehouse end RUB</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>{"warehouse": "Склад Мокеева", "in_rub": 12520673.4, "out_rub": 11129885.29, "end_rub": 1390788.11}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>live/evidence/h4_integrate_20260724/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>finding</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>H4: W4 refresh 2826 sales / 806 settlements (33 bank-linked); SKU cover cost 368/sales 738/∩ 257; fabric SKUs 1728 end~None.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>H3 — 14 новых документов</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-24 16:18 | Controlled Staging | NEW LE Салон Юлия Янина</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Метрика</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Значение</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>catalog</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>LE-IP-YANINA, LE-OOO-DEKOR, LE-OOO-SALON-YANINA</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sber payments</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sber OUT/IN RUB</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>5516593.99 / 4923673.51</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Card StatementFull</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>417 | ['Мамушкина Е.А.']</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SKU master</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1863</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sales lines B2B/IM/TSUM</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>{"B2B": 230, "IM": 1852, "TSUM": 744}</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Sales revenue RUB</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>{"B2B": 13897226.09, "IM": 56736038.01, "TSUM": 122849275.56}</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Fabric end stock RUB</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>23502565.09</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>RACI draft</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Мамушкина Елена / Сливяк Галина — нужен ACCEPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>live/evidence/h3_new_docs_20260724/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>finding</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>H3: +14 files → catalog 107; NEW LE Салон Янина; Sber 510 pays; card 417 (holder Мамушкина); SKU master 1863; sales ext 2826; RACI draft Мамушкина/Сливяк.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>H2 Enrichment — USN amounts + settle backfill + signer candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Updated: 2026-07-24 16:12 | NOT SoT | RACI still required</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Метрика</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Значение</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>settle backfill</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>{"applied": 8, "by_conf": {"HIGH": 6, "MED": 2}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SUP fuzzy HIGH</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>{"candidates": 2, "by_conf": {"HIGH": 2}, "out_rub": 73929.52}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>USN amounts extracted</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>signer candidates</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ЯНИН ЕВГЕНИЙ НИКОЛАЕВИЧ, ЯНИНА ЮЛИЯ ФЕДОРОВНА</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>usn obligations patched</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>live/evidence/h2_enrichment_20260724/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>finding</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>H2: settle backfill {'applied': 8, 'by_conf': {'HIGH': 6, 'MED': 2}}; SUP fuzzy {'candidates': 2, 'by_conf': {'HIGH': 2}, 'out_rub': 73929.52}; USN amounts 4/4; signer candidates ['ЯНИН ЕВГЕНИЙ НИКОЛАЕВИЧ', 'ЯНИНА ЮЛИЯ ФЕДОРОВНА'].</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>next</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Confirm signer candidate(s) in Owner Packet → fill RACI → SoT gate</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>H1 Spine Links — post W1–W6 hardening</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Updated: 2026-07-24 16:08 | NOT SoT</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Метрика</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Значение</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SUP with INN matched in bank</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>28/44</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SUP payment edges (OUT)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SUP matched OUT RUB</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>54740292.94</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SETTLE↔bank by doc_num</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>by confidence</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>{"LOW": 6, "HIGH": 6, "MED": 2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>live/evidence/h1_spine_links_20260724/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>finding</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>H1: SUP.inn↔bank 28/44 INN, 304 out edges (~54740293 RUB); SETTLE↔bank by doc_num: 6 ({'LOW': 6}).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>next</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>H1: SUP.inn↔bank 28/44 INN, 304 out edges (~54740293 RUB); SETTLE↔bank by doc_num: 14 ({'LOW': 6, 'HIGH': 6, 'MED': 2}).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>by_method</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>{"doc_num_in_purpose": 6, "amount_name_same_month": 8}</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>YANINA W6 TAX/BUD — Controlled Staging</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Updated: 2026-07-24 16:04 | NOT SoT — RACI gate still blocks</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Метрика</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Значение</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>tax_obligations</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>tax_by_type</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>{"6NDFL": 5, "NDS": 5, "USN": 4, "RSV": 6, "ENS": 2, "REPORT_LIST": 3}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>DEKOR INN</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>7735518240</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>tax_cash_lines</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>bank_tax_budget_payments</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>tax_cash↔bank</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>{"GAP": 1, "CLOSE": 26, "SOFT_GAP": 3}</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>tax CLOSE/SOFT months</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>budget_lines</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>bud_exp↔DDS</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>{"DDS_ONLY": 25, "CLOSE": 2, "SOFT_GAP": 1, "GAP": 2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>bud CLOSE/SOFT</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-01, 2026-02, 2026-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>bud_payroll↔W2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>{"GAP": 2, "SOFT_GAP": 2, "CLOSE": 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>live/evidence/w6_tax_bud_20260724/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>registers</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>live/registers/w6_tax_bud/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>finding</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>W6: 25 tax obligations ({'6NDFL': 5, 'NDS': 5, 'USN': 4, 'RSV': 6, 'ENS': 2, 'REPORT_LIST': 3}); tax_cash↔bank: {'GAP': 1, 'CLOSE': 26, 'SOFT_GAP': 3}; budget 475 lines; bud_exp↔DDS: {'DDS_ONLY': 25, 'CLOSE': 2, 'SOFT_GAP': 1, 'GAP': 2}; bud_payroll↔W2: {'GAP': 2, 'SOFT_GAP': 2, 'CLOSE': 1}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>next</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>RACI/SoT gate; optional deep PDF amount extract; SUP.inn→bank match</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>recon_tax_cash_bank (sample recent)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>period_month</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>tax_cash_rub</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>bank_tax_like_rub</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>delta</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>444228.63</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>444228.63</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>741644.66</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>741644.66</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>883006.92</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>878906.92</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>4100.0</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>3809031.94</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>3804197.94</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>4834.0</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>599816.64</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>599816.64</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>775148.87</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>775148.87</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2948598.18</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2906598.18</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>42000.0</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1470436.95</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1393026.95</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>77410.0</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>SOFT_GAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1267928.63</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1267928.63</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2257284.46</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2221784.46</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>35500.0</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>1528446.62</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1528446.62</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1828724.89</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1828724.89</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>1718264.68</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1672113.41</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>46151.27</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>475944.0</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>475944.0</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>3201097.69</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>3201097.69</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>4076718.89</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>4076718.89</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>-0.0</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1646534.41</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1646534.41</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>288670.11</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>319570.11</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>-30900.0</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>SOFT_GAP</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4034,7 +4356,78 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>H34 CFO Memo + Phase C Design</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-24 20:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>H34: CFO executive memo + 15-min meeting script + Phase C unified income DESIGN ONLY (no P&amp;L build). Consulting complete until owner decisions/files.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Memo</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>live/CFO_EXEC_MEMO.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Phase C</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>live/PHASE_C_UNIFIED_INCOME_DESIGN.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Script</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>live/MEETING_15MIN_SCRIPT.md</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4209,7 +4602,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4408,7 +4801,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4583,7 +4976,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4732,7 +5125,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5068,54 +5461,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>H29 MD / Individual sewing channel</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-07-24 19:35</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>H29: MD_INDIVIDUAL channel from SALES DDS Salon+Shop; MD_INDIVIDUAL=83.9% (brief 83.0%), TSUM_B2B=8.0% (brief 9.0%), IM=7.7% (brief 8.0%); MD opex months=29. Goods marts unchanged.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Doc</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>live/MD_CHANNEL.md</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10957,7 +11303,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11677,7 +12023,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12599,7 +12945,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15932,7 +16278,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16922,7 +17268,88 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>H33 Owner Briefing Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-24 19:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Consulting→action. No register rebuild.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Doc</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>live/OWNER_BRIEFING_PACK.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>live/YANINA_OWNER_BRIEFING_PACK.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>IM open</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>B2B open</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>15 / 2.51M RUB</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17020,7 +17447,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -18143,7 +18570,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -18415,7 +18842,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -18457,85 +18884,6 @@
       <c r="B3" t="inlineStr">
         <is>
           <t>6-НДФЛ (с 2021 года) за 2025 г. (Янина Ю. Ф. ИП)(1).pdf (a8fcdd6b) | 6-НДФЛ (с 2021 года) за 2025 г. (Янина Ю. Ф. ИП).pdf (a8fcdd6b)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>H28 TSUM COGS split</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-07-24 19:32</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>H28: TSUM dual view — reported margin 37.9% vs product(W3) 87.9%; commission proxy 60,954,243 ₽ (~50.1% rev) vs agency@net-rate 65,503,234 ₽. No double-count policy set.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Reported GM%</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>37.9</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Product GM%</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>87.90000000000001</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Comm proxy / Agency model</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>60,954,243 / 65,503,234</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Doc</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>live/TSUM_COGS_SPLIT.md</t>
         </is>
       </c>
     </row>
@@ -18550,27 +18898,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>H27 Business Structure</t>
+          <t>H32 Project Handoff</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-24 19:29</t>
+          <t>2026-07-24 19:38</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H27: business structure ingested; 10 RACI stubs→real FIO; 7 model flags (P0: TSUM commission in COGS; channel mix 83/8/9; Decor wind-down). See live/BUSINESS_STRUCTURE.md</t>
+          <t>H32: project handoff published (HANDOFF.md). Autonomous data work paused until commit or new files.</t>
         </is>
       </c>
     </row>
@@ -18582,31 +18930,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>live/BUSINESS_STRUCTURE.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>P0 flag</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>TSUM commission inside COGS</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Channel mix 2025</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>83% individual / 8% IM / 9% B2B(TSUM)</t>
+          <t>HANDOFF.md</t>
         </is>
       </c>
     </row>
@@ -18621,69 +18945,39 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>H25 Domain Ops</t>
+          <t>H31 Executive + MD recon fix</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-24 19:29</t>
+          <t>2026-07-24 19:38</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H25: 14 gap rows → 14 assigned (real=14, stub=0), open=0. Open domain asks: 0.</t>
+          <t>H31: 2024-01 → CLOSE after excluding Казьмина −70k adj; 2026-06 → DDS_LAG; MD recon ≥2024 CLOSE+SOFT 29/30 (+1 lag). Executive dashboard published.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Gap rows</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Assigned (accepted owners)</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Need open-domain FIO</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Pack</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>live/YANINA_DOMAIN_OPS_H25.xlsx</t>
+          <t>Doc</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>live/EXEC_DASHBOARD.md</t>
         </is>
       </c>
     </row>
@@ -18702,45 +18996,45 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
-        <is>
-          <t>H26 Temporary Owner Stubs</t>
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>H30 MD workbook parse</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-24 19:26</t>
+          <t>2026-07-24 19:37</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H26: 10 RACI stubs (ACCEPT_STUB); alias candidates under Product stub; domain board rebuilt — 14/14 gaps have owner fio (2 on stubs). Replace stubs with real FIO.</t>
+          <t>H30: MD workbook parsed — payments 6663, salon 4194, shop 11173; 2025 payments 2,319,617 EUR vs DDS Salon+Shop 2,325,846 (gap -6,229); recon CLOSE+SOFT 28/30 since 2024.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Stubs applied</t>
+          <t>2025 gap EUR</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>-6229</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Replace with real FIO</t>
+          <t>Doc</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>YES — required</t>
+          <t>live/MD_WORKBOOK.md</t>
         </is>
       </c>
     </row>
@@ -18755,48 +19049,40 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>H24 SKU Alias Master</t>
+          <t>H29 MD / Individual sewing channel</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-24 19:22</t>
+          <t>2026-07-24 19:35</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H24: sku_alias_master created — 16 controlled candidates (pending Product Owner), 4 accepted exception/quarantine rows from H23.</t>
+          <t>H29: MD_INDIVIDUAL channel from SALES DDS Salon+Shop; MD_INDIVIDUAL=83.9% (brief 83.0%), TSUM_B2B=8.0% (brief 9.0%), IM=7.7% (brief 8.0%); MD opex months=29. Goods marts unchanged.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Candidates</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Accepted rows</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>4</v>
+          <t>Doc</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>live/MD_CHANNEL.md</t>
+        </is>
       </c>
     </row>
   </sheetData>
